--- a/data/trans_dic/P2B_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P2B_R-Estudios-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con personas que requieren dedicación o cuidados especiales</t>
+          <t>Hogares con personas que requieren dedicación o cuidados especiales (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>27,52; 47,24</t>
+          <t>26,58; 47,77</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>60,89; 80,39</t>
+          <t>60,68; 80,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>57,62; 81,34</t>
+          <t>56,0; 80,53</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>24,9; 58,65</t>
+          <t>25,5; 59,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>16,67; 35,68</t>
+          <t>17,05; 36,08</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,72; 91,16</t>
+          <t>75,12; 91,23</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,24; 86,37</t>
+          <t>65,53; 86,12</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>28,84; 50,75</t>
+          <t>29,4; 51,47</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>24,93; 39,29</t>
+          <t>24,68; 39,4</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>71,28; 84,72</t>
+          <t>71,29; 84,27</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>66,26; 81,45</t>
+          <t>66,51; 82,2</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>30,95; 51,13</t>
+          <t>30,44; 50,38</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>24,74; 32,89</t>
+          <t>24,21; 32,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>79,79; 86,71</t>
+          <t>79,93; 86,86</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>63,61; 72,0</t>
+          <t>63,54; 71,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25,77; 36,36</t>
+          <t>25,46; 36,37</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>25,53; 33,26</t>
+          <t>25,24; 33,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>80,77; 86,79</t>
+          <t>80,49; 86,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>62,3; 70,74</t>
+          <t>62,68; 70,56</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>33,08; 42,53</t>
+          <t>32,78; 42,66</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>26,22; 31,99</t>
+          <t>26,13; 31,96</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>81,29; 86,07</t>
+          <t>81,26; 85,99</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>64,5; 70,02</t>
+          <t>64,26; 69,92</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>31,08; 38,06</t>
+          <t>31,13; 38,21</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>30,1; 43,69</t>
+          <t>30,1; 43,11</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>78,62; 90,02</t>
+          <t>79,34; 89,9</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>60,67; 73,82</t>
+          <t>61,27; 74,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>19,73; 30,94</t>
+          <t>18,98; 31,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>28,33; 42,4</t>
+          <t>28,41; 42,3</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>75,88; 86,83</t>
+          <t>75,76; 87,0</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>69,42; 81,37</t>
+          <t>69,49; 81,74</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19,77; 31,34</t>
+          <t>19,44; 31,47</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>31,07; 40,27</t>
+          <t>31,08; 40,7</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>79,35; 87,0</t>
+          <t>79,5; 87,33</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>66,76; 76,08</t>
+          <t>67,11; 76,03</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>20,79; 28,98</t>
+          <t>20,94; 29,53</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>28,18; 35,0</t>
+          <t>28,11; 35,02</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>79,61; 85,36</t>
+          <t>79,53; 85,39</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>64,57; 71,12</t>
+          <t>64,51; 71,45</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26,44; 34,64</t>
+          <t>26,59; 34,58</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,03; 33,54</t>
+          <t>26,77; 33,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,08; 86,23</t>
+          <t>80,5; 85,83</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,34; 72,76</t>
+          <t>66,23; 72,9</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>31,04; 38,42</t>
+          <t>31,17; 38,36</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>28,41; 33,2</t>
+          <t>28,56; 33,24</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>81,2; 84,96</t>
+          <t>81,24; 84,98</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>66,74; 71,08</t>
+          <t>66,62; 71,17</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>30,08; 35,49</t>
+          <t>30,12; 35,59</t>
         </is>
       </c>
     </row>
@@ -1215,4 +1216,995 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N16"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Hogares con personas que requieren dedicación o cuidados especiales (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Primarios</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>20742</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>39578</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>28338</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>21206</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>13377</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>52707</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>38483</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>24782</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>34119</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>92285</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>66821</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>45989</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>15005; 26974</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>33669; 44916</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>22758; 32729</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>13943; 32418</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>8757; 18535</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>46639; 56647</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>32646; 42903</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>18228; 31915</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>26614; 42488</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>83820; 99083</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>60161; 74362</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>35521; 58784</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Secundarios</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>370</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>355</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>220</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>405</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>361</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>291</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>775</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>716</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>475</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>88297</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>254744</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>232004</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>147169</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>103824</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>284546</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>249436</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>190467</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>192121</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>539290</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>481439</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>337636</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>75118; 101135</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>243497; 264626</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>217397; 245778</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>116739; 166779</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>89272; 117514</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>273002; 294321</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>234856; 264379</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>168891; 219775</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>173506; 212216</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>523154; 553605</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>460632; 501198</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>303087; 372091</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Universitarios</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>299</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>288</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>50057</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>99483</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>90604</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>36309</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>42837</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>112547</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>103753</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>45886</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>92894</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>212030</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>194357</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>82194</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>41117; 58876</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>92689; 105028</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>81651; 99750</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>28275; 46534</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>35100; 52252</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>103708; 119104</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>95335; 112140</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>35394; 57319</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>80838; 105883</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>201722; 221585</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>181513; 205638</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>69313; 97774</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>569</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>535</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>305</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>639</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>571</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>352</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>479</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1208</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>1106</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>657</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>159096</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>393806</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>350945</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>204684</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>160038</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>449801</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>391673</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>261135</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>319134</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>843606</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>742618</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>465819</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>141510; 176257</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>379315; 407294</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>332904; 368716</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>176087; 228995</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>141508; 176911</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>433225; 461879</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>372009; 409489</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>236671; 291279</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>294665; 343019</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>824703; 862665</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>717982; 767086</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>428119; 505938</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="8">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/P2B_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P2B_R-Estudios-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>26,58; 47,77</t>
+          <t>26,72; 47,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>60,68; 80,95</t>
+          <t>60,05; 79,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>56,0; 80,53</t>
+          <t>57,14; 80,66</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25,5; 59,29</t>
+          <t>25,15; 58,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,05; 36,08</t>
+          <t>17,72; 36,79</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,12; 91,23</t>
+          <t>75,8; 90,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>65,53; 86,12</t>
+          <t>66,05; 86,14</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>29,4; 51,47</t>
+          <t>30,52; 51,11</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>24,68; 39,4</t>
+          <t>24,84; 39,38</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>71,29; 84,27</t>
+          <t>72,13; 84,56</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>66,51; 82,2</t>
+          <t>65,39; 80,99</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>30,44; 50,38</t>
+          <t>30,68; 50,74</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>24,21; 32,59</t>
+          <t>24,29; 32,37</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>79,93; 86,86</t>
+          <t>79,68; 86,89</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>63,54; 71,84</t>
+          <t>63,84; 71,63</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25,46; 36,37</t>
+          <t>26,06; 36,43</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>25,24; 33,23</t>
+          <t>25,59; 33,41</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>80,49; 86,78</t>
+          <t>80,69; 86,94</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>62,68; 70,56</t>
+          <t>62,66; 70,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>32,78; 42,66</t>
+          <t>32,9; 42,25</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>26,13; 31,96</t>
+          <t>25,71; 31,54</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>81,26; 85,99</t>
+          <t>81,13; 86,16</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>64,26; 69,92</t>
+          <t>64,16; 70,0</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>31,13; 38,21</t>
+          <t>30,89; 37,89</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>30,1; 43,11</t>
+          <t>30,27; 43,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>79,34; 89,9</t>
+          <t>79,33; 90,02</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>61,27; 74,85</t>
+          <t>61,32; 73,9</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18,98; 31,24</t>
+          <t>18,71; 31,06</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>28,41; 42,3</t>
+          <t>28,31; 41,58</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>75,76; 87,0</t>
+          <t>76,26; 87,75</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>69,49; 81,74</t>
+          <t>68,89; 80,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19,44; 31,47</t>
+          <t>19,41; 31,18</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>31,08; 40,7</t>
+          <t>31,24; 40,98</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>79,5; 87,33</t>
+          <t>79,48; 87,37</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>67,11; 76,03</t>
+          <t>67,01; 76,09</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>20,94; 29,53</t>
+          <t>20,87; 29,07</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>28,11; 35,02</t>
+          <t>28,48; 34,87</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>79,53; 85,39</t>
+          <t>79,67; 85,52</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>64,51; 71,45</t>
+          <t>64,84; 71,83</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26,59; 34,58</t>
+          <t>26,93; 34,74</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>26,77; 33,47</t>
+          <t>27,52; 34,08</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>80,5; 85,83</t>
+          <t>81,05; 86,03</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,23; 72,9</t>
+          <t>66,42; 72,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>31,17; 38,36</t>
+          <t>30,85; 38,18</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>28,56; 33,24</t>
+          <t>28,59; 33,27</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>81,24; 84,98</t>
+          <t>81,03; 84,86</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>66,62; 71,17</t>
+          <t>66,66; 71,2</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>30,12; 35,59</t>
+          <t>30,04; 35,56</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>15005; 26974</t>
+          <t>15086; 26977</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>33669; 44916</t>
+          <t>33320; 44209</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>22758; 32729</t>
+          <t>23220; 32781</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13943; 32418</t>
+          <t>13754; 31989</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>8757; 18535</t>
+          <t>9103; 18901</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>46639; 56647</t>
+          <t>47066; 56448</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32646; 42903</t>
+          <t>32907; 42914</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>18228; 31915</t>
+          <t>18923; 31690</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>26614; 42488</t>
+          <t>26784; 42469</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>83820; 99083</t>
+          <t>84807; 99417</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>60161; 74362</t>
+          <t>59152; 73263</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>35521; 58784</t>
+          <t>35796; 59200</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>75118; 101135</t>
+          <t>75380; 100456</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>243497; 264626</t>
+          <t>242738; 264712</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>217397; 245778</t>
+          <t>218411; 245064</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>116739; 166779</t>
+          <t>119500; 167040</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>89272; 117514</t>
+          <t>90492; 118167</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>273002; 294321</t>
+          <t>273686; 294881</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>234856; 264379</t>
+          <t>234788; 265483</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>168891; 219775</t>
+          <t>169526; 217673</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>173506; 212216</t>
+          <t>170726; 209414</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>523154; 553605</t>
+          <t>522318; 554690</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>460632; 501198</t>
+          <t>459912; 501759</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>303087; 372091</t>
+          <t>300778; 368967</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>41117; 58876</t>
+          <t>41343; 59487</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>92689; 105028</t>
+          <t>92681; 105163</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>81651; 99750</t>
+          <t>81719; 98484</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>28275; 46534</t>
+          <t>27869; 46272</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>35100; 52252</t>
+          <t>34974; 51364</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>103708; 119104</t>
+          <t>104396; 120132</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>95335; 112140</t>
+          <t>94516; 110659</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>35394; 57319</t>
+          <t>35348; 56790</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>80838; 105883</t>
+          <t>81261; 106588</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>201722; 221585</t>
+          <t>201665; 221682</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>181513; 205638</t>
+          <t>181243; 205790</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>69313; 97774</t>
+          <t>69089; 96244</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>141510; 176257</t>
+          <t>143346; 175521</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>379315; 407294</t>
+          <t>380002; 407906</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>332904; 368716</t>
+          <t>334612; 370677</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>176087; 228995</t>
+          <t>178285; 230011</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>141508; 176911</t>
+          <t>145465; 180130</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>433225; 461879</t>
+          <t>436171; 462974</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>372009; 409489</t>
+          <t>373103; 409824</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>236671; 291279</t>
+          <t>234238; 289888</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>294665; 343019</t>
+          <t>295036; 343331</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>824703; 862665</t>
+          <t>822566; 861399</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>717982; 767086</t>
+          <t>718387; 767403</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>428119; 505938</t>
+          <t>427021; 505411</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P2B_R-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P2B_R-Estudios-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>26,04%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>84,89%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>77,24%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>41,03%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>36,74%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>71,33%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>69,73%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>38,78%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>26,04%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>84,89%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>77,24%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>37,03%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>39,22%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>26,72; 47,78</t>
+          <t>16,67; 35,68</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>60,05; 79,68</t>
+          <t>75,72; 91,16</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>57,14; 80,66</t>
+          <t>66,24; 86,37</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>25,15; 58,5</t>
+          <t>29,54; 51,99</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>17,72; 36,79</t>
+          <t>27,52; 47,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>75,8; 90,91</t>
+          <t>60,89; 80,39</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,05; 86,14</t>
+          <t>57,62; 81,34</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>30,52; 51,11</t>
+          <t>26,12; 49,74</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>24,84; 39,38</t>
+          <t>24,93; 39,29</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>72,13; 84,56</t>
+          <t>71,28; 84,72</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>65,39; 80,99</t>
+          <t>66,26; 81,45</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>30,68; 50,74</t>
+          <t>31,68; 48,64</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>29,36%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>83,9%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>66,57%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>37,96%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>28,45%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>83,62%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>67,81%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>32,1%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>29,36%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>83,9%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>66,57%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>36,97%</t>
+          <t>34,54%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>36,33%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>24,29; 32,37</t>
+          <t>25,53; 33,26</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>79,68; 86,89</t>
+          <t>80,77; 86,79</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>63,84; 71,63</t>
+          <t>62,3; 70,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>26,06; 36,43</t>
+          <t>33,94; 43,56</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>25,59; 33,41</t>
+          <t>24,74; 32,89</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>80,69; 86,94</t>
+          <t>79,79; 86,71</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>62,66; 70,85</t>
+          <t>63,61; 72,0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>32,9; 42,25</t>
+          <t>31,02; 39,08</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>25,71; 31,54</t>
+          <t>26,22; 31,99</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>81,13; 86,16</t>
+          <t>81,29; 86,07</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>64,16; 70,0</t>
+          <t>64,5; 70,02</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>30,89; 37,89</t>
+          <t>33,43; 39,48</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>34,67%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>82,21%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>75,62%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>26,23%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>36,65%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>85,15%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>67,99%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>24,37%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>34,67%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>82,21%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>75,62%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>23,96%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>24,83%</t>
+          <t>25,16%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>30,27; 43,55</t>
+          <t>28,33; 42,4</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>79,33; 90,02</t>
+          <t>75,88; 86,83</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>61,32; 73,9</t>
+          <t>69,42; 81,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>18,71; 31,06</t>
+          <t>20,43; 32,68</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>28,31; 41,58</t>
+          <t>30,1; 43,69</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>76,26; 87,75</t>
+          <t>78,62; 90,02</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>68,89; 80,66</t>
+          <t>60,67; 73,82</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>19,41; 31,18</t>
+          <t>19,36; 30,51</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>31,24; 40,98</t>
+          <t>31,07; 40,27</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>79,48; 87,37</t>
+          <t>79,35; 87,0</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>67,01; 76,09</t>
+          <t>66,76; 76,08</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>20,87; 29,07</t>
+          <t>21,16; 29,27</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>30,28%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>83,58%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>69,73%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>35,4%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>31,61%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>82,57%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>68,01%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>30,91%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>30,28%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>83,58%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>69,73%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>34,39%</t>
+          <t>32,2%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>33,89%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>28,48; 34,87</t>
+          <t>27,03; 33,54</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>79,67; 85,52</t>
+          <t>81,08; 86,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>64,84; 71,83</t>
+          <t>66,34; 72,76</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>26,93; 34,74</t>
+          <t>31,94; 39,04</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>27,52; 34,08</t>
+          <t>28,18; 35,0</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>81,05; 86,03</t>
+          <t>79,61; 85,36</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>66,42; 72,96</t>
+          <t>64,57; 71,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>30,85; 38,18</t>
+          <t>29,03; 35,27</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>28,59; 33,27</t>
+          <t>28,41; 33,2</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>81,03; 84,86</t>
+          <t>81,2; 84,96</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>66,66; 71,2</t>
+          <t>66,74; 71,08</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>30,04; 35,56</t>
+          <t>31,6; 36,51</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1260,7 +1260,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1368,42 +1368,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>31</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>58</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>46</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>28</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>76</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>56</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1436,42 +1436,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>13377</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>52707</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>38483</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>23275</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>20742</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>39578</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>28338</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>21206</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>13377</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>52707</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>38483</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>24782</t>
+          <t>17315</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>45989</t>
+          <t>40590</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>15086; 26977</t>
+          <t>8564; 18331</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>33320; 44209</t>
+          <t>47016; 56599</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>23220; 32781</t>
+          <t>33001; 43030</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>13754; 31989</t>
+          <t>16759; 29496</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>9103; 18901</t>
+          <t>15540; 26674</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>47066; 56448</t>
+          <t>33783; 44602</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>32907; 42914</t>
+          <t>23419; 33059</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>18923; 31690</t>
+          <t>12215; 23257</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>26784; 42469</t>
+          <t>26878; 42365</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>84807; 99417</t>
+          <t>83804; 99605</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>59152; 73263</t>
+          <t>59937; 73678</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>35796; 59200</t>
+          <t>32781; 50343</t>
         </is>
       </c>
     </row>
@@ -1576,42 +1576,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>405</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>361</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>255</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>135</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>370</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>355</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>220</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>156</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>405</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>361</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>255</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -1644,42 +1644,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>103824</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>284546</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>249436</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>180110</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>88297</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>254744</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>232004</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>147169</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>103824</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>284546</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>249436</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>190467</t>
+          <t>148794</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>337636</t>
+          <t>328905</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>75380; 100456</t>
+          <t>90272; 117629</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>242738; 264712</t>
+          <t>273951; 294350</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>218411; 245064</t>
+          <t>233461; 265073</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>119500; 167040</t>
+          <t>161010; 206673</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>90492; 118167</t>
+          <t>76769; 102055</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>273686; 294881</t>
+          <t>243090; 264162</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>234788; 265483</t>
+          <t>217644; 246338</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>169526; 217673</t>
+          <t>133645; 168392</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>170726; 209414</t>
+          <t>174107; 212398</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>522318; 554690</t>
+          <t>523339; 554142</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>459912; 501759</t>
+          <t>462327; 501945</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>300778; 368967</t>
+          <t>302614; 357423</t>
         </is>
       </c>
     </row>
@@ -1784,42 +1784,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>73</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>141</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>134</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>57</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>158</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>154</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>60</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1852,42 +1852,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>42837</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>112547</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>103753</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>43869</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>50057</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>99483</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>90604</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>36309</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>42837</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>112547</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>103753</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>45886</t>
+          <t>35786</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>82194</t>
+          <t>79655</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>41343; 59487</t>
+          <t>34997; 52388</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>92681; 105163</t>
+          <t>103879; 118862</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>81719; 98484</t>
+          <t>95238; 111643</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>27869; 46272</t>
+          <t>34178; 54659</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>34974; 51364</t>
+          <t>41106; 59676</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>104396; 120132</t>
+          <t>91852; 105169</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>94516; 110659</t>
+          <t>80851; 98374</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>35348; 56790</t>
+          <t>28916; 45578</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>81261; 106588</t>
+          <t>80812; 104740</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>201665; 221682</t>
+          <t>201342; 220733</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>181243; 205790</t>
+          <t>180568; 205760</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>69089; 96244</t>
+          <t>67002; 92685</t>
         </is>
       </c>
     </row>
@@ -1992,42 +1992,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>240</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>639</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>571</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>352</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>239</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>569</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>535</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>305</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>240</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>639</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>571</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>352</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2060,42 +2060,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>160038</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>449801</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>391673</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>247254</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>159096</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>393806</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>350945</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>204684</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>160038</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>449801</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>391673</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>261135</t>
+          <t>201895</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>465819</t>
+          <t>449149</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>143346; 175521</t>
+          <t>142875; 177263</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>380002; 407906</t>
+          <t>436342; 464031</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>334612; 370677</t>
+          <t>372627; 408700</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>178285; 230011</t>
+          <t>223101; 272696</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>145465; 180130</t>
+          <t>141828; 176193</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>436171; 462974</t>
+          <t>379722; 407139</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>373103; 409824</t>
+          <t>333199; 367020</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>234238; 289888</t>
+          <t>181994; 221161</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>295036; 343331</t>
+          <t>293215; 342599</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>822566; 861399</t>
+          <t>824311; 862397</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>718387; 767403</t>
+          <t>719347; 766056</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>427021; 505411</t>
+          <t>418762; 483949</t>
         </is>
       </c>
     </row>
